--- a/ch_03_data_viz_seaborn/ch_03_solution.xlsx
+++ b/ch_03_data_viz_seaborn/ch_03_solution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30103"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_03_data_viz_seaborn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02690C66-CE37-4C7D-833A-76C91E10B5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA36536E-BCCA-4818-943B-53BCDDF22829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1507,55 +1507,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>8467</xdr:colOff>
-      <xdr:row>363</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>42333</xdr:colOff>
-      <xdr:row>378</xdr:row>
-      <xdr:rowOff>33866</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Picture 27" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D91B85D5-5703-C997-28E6-8DFF196A569E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A364"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="821267" y="67415833"/>
-          <a:ext cx="2700866" cy="2700866"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>156634</xdr:colOff>
       <xdr:row>382</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
@@ -1585,7 +1536,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1683,7 +1634,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1732,7 +1683,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1781,7 +1732,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1790,6 +1741,55 @@
         <a:xfrm>
           <a:off x="0" y="59888967"/>
           <a:ext cx="3496733" cy="2263325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>431032</xdr:colOff>
+      <xdr:row>363</xdr:row>
+      <xdr:rowOff>23093</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>46182</xdr:colOff>
+      <xdr:row>380</xdr:row>
+      <xdr:rowOff>102629</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94AC8A08-A0E7-F958-71B7-407459BB17EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A364"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1246910" y="67079093"/>
+          <a:ext cx="3186545" cy="3219900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/ch_03_data_viz_seaborn/ch_03_solution.xlsx
+++ b/ch_03_data_viz_seaborn/ch_03_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30103"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_03_data_viz_seaborn\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_03_data_viz_seaborn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA36536E-BCCA-4818-943B-53BCDDF22829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4C660D-9FA4-46FB-BB80-5B5C5811AF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mpg" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="25">
+  <futureMetadata name="XLRICHVALUE" count="23">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -210,27 +210,13 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="25"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="26"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="25">
+  <valueMetadata count="23">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -300,12 +286,6 @@
     <bk>
       <rc t="2" v="22"/>
     </bk>
-    <bk>
-      <rc t="2" v="23"/>
-    </bk>
-    <bk>
-      <rc t="2" v="24"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
@@ -366,23 +346,17 @@
       <code>sns.violinplot(x='origin', y='mpg', data=mpg_df)</code>
     </pythonScript>
     <pythonScript>
-      <code>sns.kdeplot(x='mpg', data=mpg_df, fill=True)</code>
-    </pythonScript>
-    <pythonScript>
-      <code>sns.kdeplot(y='mpg', hue='origin', data=mpg_df, fill=True)</code>
-    </pythonScript>
-    <pythonScript>
-      <code>sns.scatterplot(x='weight', y='mpg', data=mpg_df)</code>
-    </pythonScript>
-    <pythonScript>
-      <code>sns.scatterplot(x='weight', y='mpg', hue='origin', data=mpg_df)</code>
-    </pythonScript>
-    <pythonScript>
       <code>sns.stripplot(x='origin', y='mpg', data=mpg_df)</code>
     </pythonScript>
     <pythonScript>
       <code># Add jitter and transparency to data points
 sns.stripplot(x='origin', y='mpg', data=mpg_df, jitter=0.2, alpha=0.7)</code>
+    </pythonScript>
+    <pythonScript>
+      <code xml:space="preserve">sns.scatterplot(x='weight', y='mpg', data=mpg_df) </code>
+    </pythonScript>
+    <pythonScript>
+      <code xml:space="preserve">sns.scatterplot(x='weight', y='mpg', hue='origin', data=mpg_df) </code>
     </pythonScript>
     <pythonScript>
       <code>sns.pairplot(mpg_df, vars=['mpg', 'horsepower', 'weight', 'acceleration'])</code>
@@ -575,55 +549,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>73501</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>127516</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CA627BF-1817-4F0A-82A9-22C9545FC6D2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A1"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12869333" y="4732867"/>
-          <a:ext cx="5221234" cy="3950216"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>59267</xdr:colOff>
       <xdr:row>9</xdr:row>
@@ -654,7 +579,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -703,7 +628,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -752,7 +677,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -801,7 +726,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -821,210 +746,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>165101</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>419101</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>167379</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC458221-10A6-72B2-E1F2-7EB618B6C46D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A101"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="808568" y="19490267"/>
-          <a:ext cx="2921000" cy="2157046"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>55033</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>797277</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>8467</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FA1744E-8677-7CA2-394E-5226EEC017F1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A114"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="698500" y="22741467"/>
-          <a:ext cx="3409244" cy="2556933"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>109008</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>101601</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECFD18A3-E1D7-856F-3A67-0C9A841EF149}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A132"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="25120601"/>
-          <a:ext cx="2979208" cy="2286000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>146</xdr:row>
-      <xdr:rowOff>21167</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>565992</xdr:colOff>
-      <xdr:row>159</xdr:row>
-      <xdr:rowOff>135467</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86DB02BB-41EF-15DA-E1E4-5B49E48C7219}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A147"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="643467" y="27872267"/>
-          <a:ext cx="3232992" cy="2480733"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>161</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>160866</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>175</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>136339</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1040,13 +769,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A163"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A99"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1067,13 +796,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>537634</xdr:colOff>
-      <xdr:row>179</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>876389</xdr:colOff>
-      <xdr:row>191</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1089,13 +818,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A181"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A117"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1116,13 +845,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>622301</xdr:colOff>
-      <xdr:row>194</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>694267</xdr:colOff>
-      <xdr:row>213</xdr:row>
+      <xdr:row>173</xdr:row>
       <xdr:rowOff>93134</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1138,13 +867,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A195"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A155"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1165,13 +894,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>596901</xdr:colOff>
-      <xdr:row>215</xdr:row>
+      <xdr:row>175</xdr:row>
       <xdr:rowOff>165101</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>613187</xdr:colOff>
-      <xdr:row>233</xdr:row>
+      <xdr:row>193</xdr:row>
       <xdr:rowOff>42335</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1187,13 +916,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A217"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A177"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1214,13 +943,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>110067</xdr:colOff>
-      <xdr:row>246</xdr:row>
+      <xdr:row>206</xdr:row>
       <xdr:rowOff>84667</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>523608</xdr:colOff>
-      <xdr:row>260</xdr:row>
+      <xdr:row>220</xdr:row>
       <xdr:rowOff>67734</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1236,13 +965,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A247"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A207"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1263,13 +992,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>71967</xdr:colOff>
-      <xdr:row>262</xdr:row>
+      <xdr:row>222</xdr:row>
       <xdr:rowOff>29633</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>198967</xdr:colOff>
-      <xdr:row>274</xdr:row>
+      <xdr:row>234</xdr:row>
       <xdr:rowOff>141292</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1285,13 +1014,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A263"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A223"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1312,13 +1041,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>279</xdr:row>
+      <xdr:row>239</xdr:row>
       <xdr:rowOff>80434</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>828443</xdr:colOff>
-      <xdr:row>290</xdr:row>
+      <xdr:row>250</xdr:row>
       <xdr:rowOff>173567</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1334,13 +1063,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A280"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A240"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1361,13 +1090,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>110067</xdr:colOff>
-      <xdr:row>294</xdr:row>
+      <xdr:row>254</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>731985</xdr:colOff>
-      <xdr:row>304</xdr:row>
+      <xdr:row>264</xdr:row>
       <xdr:rowOff>59267</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1383,13 +1112,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A295"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A255"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1410,13 +1139,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>347135</xdr:colOff>
-      <xdr:row>309</xdr:row>
+      <xdr:row>269</xdr:row>
       <xdr:rowOff>169335</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>503767</xdr:colOff>
-      <xdr:row>327</xdr:row>
+      <xdr:row>287</xdr:row>
       <xdr:rowOff>1428</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1432,13 +1161,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A310"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A270"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1459,13 +1188,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>270934</xdr:colOff>
-      <xdr:row>345</xdr:row>
+      <xdr:row>305</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>374582</xdr:colOff>
-      <xdr:row>359</xdr:row>
+      <xdr:row>319</xdr:row>
       <xdr:rowOff>103298</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1481,13 +1210,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A346"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A306"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1508,13 +1237,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>156634</xdr:colOff>
-      <xdr:row>382</xdr:row>
+      <xdr:row>342</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>699024</xdr:colOff>
-      <xdr:row>396</xdr:row>
+      <xdr:row>356</xdr:row>
       <xdr:rowOff>46566</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1530,13 +1259,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A383"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A343"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1585,7 +1314,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1634,7 +1363,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1683,7 +1412,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1704,13 +1433,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>329</xdr:row>
+      <xdr:row>289</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>16933</xdr:colOff>
-      <xdr:row>341</xdr:row>
+      <xdr:row>301</xdr:row>
       <xdr:rowOff>78925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1726,13 +1455,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A330"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A290"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1753,13 +1482,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>431032</xdr:colOff>
-      <xdr:row>363</xdr:row>
+      <xdr:row>323</xdr:row>
       <xdr:rowOff>23093</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>46182</xdr:colOff>
-      <xdr:row>380</xdr:row>
+      <xdr:row>340</xdr:row>
       <xdr:rowOff>102629</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1775,13 +1504,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A364"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A324"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1790,6 +1519,104 @@
         <a:xfrm>
           <a:off x="1246910" y="67079093"/>
           <a:ext cx="3186545" cy="3219900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>484297</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED7C1391-6933-7468-ACCC-A1C60615BF7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A131"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="581025" y="23431500"/>
+          <a:ext cx="2470260" cy="1895475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>766762</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>707274</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6F8050A-EC48-5F1F-EB14-D5DECAE56A24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="dataviz!A143"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="766762" y="25650825"/>
+          <a:ext cx="2507500" cy="1924050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1957,7 +1784,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="27">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="25">
   <rv s="0">
     <v>0</v>
   </rv>
@@ -2086,16 +1913,6 @@
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="3">
-    <v>22</v>
-    <v>9</v>
-    <v>Image generated by Python</v>
-  </rv>
-  <rv s="3">
-    <v>23</v>
-    <v>9</v>
-    <v>Image generated by Python</v>
-  </rv>
 </rvData>
 </file>
 
@@ -2190,8 +2007,6 @@
   <rel r:id="rId20"/>
   <rel r:id="rId21"/>
   <rel r:id="rId22"/>
-  <rel r:id="rId23"/>
-  <rel r:id="rId24"/>
 </richValueRels>
 </file>
 
@@ -2498,20 +2313,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M389"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12.41015625" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.234375" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="13" width="8.9375" style="3"/>
+    <col min="9" max="13" width="8.9296875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2545,7 +2360,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>32.799999999999997</v>
       </c>
@@ -2571,7 +2386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>20.100000000000001</v>
       </c>
@@ -2597,7 +2412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>22</v>
       </c>
@@ -2623,7 +2438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>24.8</v>
       </c>
@@ -2649,7 +2464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>26.9</v>
       </c>
@@ -2675,7 +2490,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>22.3</v>
       </c>
@@ -2701,7 +2516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>27.6</v>
       </c>
@@ -2727,7 +2542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>14.5</v>
       </c>
@@ -2750,7 +2565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>23.9</v>
       </c>
@@ -2776,7 +2591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>16.899999999999999</v>
       </c>
@@ -2802,7 +2617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>34.5</v>
       </c>
@@ -2828,7 +2643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>13.5</v>
       </c>
@@ -2854,7 +2669,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>41.9</v>
       </c>
@@ -2880,7 +2695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>24.4</v>
       </c>
@@ -2906,7 +2721,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>26</v>
       </c>
@@ -2932,7 +2747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>25.3</v>
       </c>
@@ -2958,7 +2773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>37.5</v>
       </c>
@@ -2984,7 +2799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>25.2</v>
       </c>
@@ -3010,7 +2825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>37.6</v>
       </c>
@@ -3036,7 +2851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>33.4</v>
       </c>
@@ -3062,7 +2877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>33.700000000000003</v>
       </c>
@@ -3088,7 +2903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>43.4</v>
       </c>
@@ -3114,7 +2929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>41.8</v>
       </c>
@@ -3140,7 +2955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>28.7</v>
       </c>
@@ -3166,7 +2981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>32.799999999999997</v>
       </c>
@@ -3192,7 +3007,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>34</v>
       </c>
@@ -3218,7 +3033,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>22.8</v>
       </c>
@@ -3244,7 +3059,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>25.4</v>
       </c>
@@ -3270,7 +3085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>14.7</v>
       </c>
@@ -3296,7 +3111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>17.3</v>
       </c>
@@ -3322,7 +3137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>20.3</v>
       </c>
@@ -3348,7 +3163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>19.7</v>
       </c>
@@ -3374,7 +3189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>20.5</v>
       </c>
@@ -3400,7 +3215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>34.9</v>
       </c>
@@ -3426,7 +3241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>23</v>
       </c>
@@ -3452,7 +3267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>31.1</v>
       </c>
@@ -3478,7 +3293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>14</v>
       </c>
@@ -3504,7 +3319,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>16.399999999999999</v>
       </c>
@@ -3530,7 +3345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>32.299999999999997</v>
       </c>
@@ -3556,7 +3371,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>20.2</v>
       </c>
@@ -3582,7 +3397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>41.9</v>
       </c>
@@ -3608,7 +3423,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>24.8</v>
       </c>
@@ -3634,7 +3449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>33</v>
       </c>
@@ -3660,7 +3475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>36.9</v>
       </c>
@@ -3686,7 +3501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>34.1</v>
       </c>
@@ -3712,7 +3527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>34.700000000000003</v>
       </c>
@@ -3738,7 +3553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>45.4</v>
       </c>
@@ -3764,7 +3579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>34.200000000000003</v>
       </c>
@@ -3790,7 +3605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>40</v>
       </c>
@@ -3816,7 +3631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>30.2</v>
       </c>
@@ -3842,7 +3657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>30.4</v>
       </c>
@@ -3868,7 +3683,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>19.399999999999999</v>
       </c>
@@ -3894,7 +3709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>16.600000000000001</v>
       </c>
@@ -3920,7 +3735,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>17.3</v>
       </c>
@@ -3946,7 +3761,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>12.5</v>
       </c>
@@ -3972,7 +3787,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>33</v>
       </c>
@@ -3998,7 +3813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>17.899999999999999</v>
       </c>
@@ -4024,7 +3839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>20.3</v>
       </c>
@@ -4050,7 +3865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>18.100000000000001</v>
       </c>
@@ -4076,7 +3891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>33.4</v>
       </c>
@@ -4102,7 +3917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>25.4</v>
       </c>
@@ -4128,7 +3943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>27</v>
       </c>
@@ -4154,7 +3969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>17.2</v>
       </c>
@@ -4180,7 +3995,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>31.1</v>
       </c>
@@ -4206,7 +4021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>20.8</v>
       </c>
@@ -4232,7 +4047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>35.799999999999997</v>
       </c>
@@ -4258,7 +4073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>23.4</v>
       </c>
@@ -4284,7 +4099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>26.5</v>
       </c>
@@ -4310,7 +4125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>27.1</v>
       </c>
@@ -4336,7 +4151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>36.4</v>
       </c>
@@ -4362,7 +4177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>31.7</v>
       </c>
@@ -4385,7 +4200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>26.1</v>
       </c>
@@ -4411,7 +4226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>42.4</v>
       </c>
@@ -4437,7 +4252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>21</v>
       </c>
@@ -4463,7 +4278,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>29.5</v>
       </c>
@@ -4489,7 +4304,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>23.7</v>
       </c>
@@ -4515,7 +4330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>12.3</v>
       </c>
@@ -4541,7 +4356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>11.7</v>
       </c>
@@ -4567,7 +4382,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>16.8</v>
       </c>
@@ -4593,7 +4408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>34.6</v>
       </c>
@@ -4619,7 +4434,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>10.9</v>
       </c>
@@ -4645,7 +4460,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>24.4</v>
       </c>
@@ -4671,7 +4486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>10.6</v>
       </c>
@@ -4697,7 +4512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>31</v>
       </c>
@@ -4723,7 +4538,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>24.1</v>
       </c>
@@ -4749,7 +4564,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>24.5</v>
       </c>
@@ -4775,7 +4590,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>35.9</v>
       </c>
@@ -4801,7 +4616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>32.200000000000003</v>
       </c>
@@ -4827,7 +4642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>29.3</v>
       </c>
@@ -4853,7 +4668,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>27.6</v>
       </c>
@@ -4879,7 +4694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>35.9</v>
       </c>
@@ -4905,7 +4720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>41.6</v>
       </c>
@@ -4931,7 +4746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>39.799999999999997</v>
       </c>
@@ -4957,7 +4772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>38.1</v>
       </c>
@@ -4983,7 +4798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>28.2</v>
       </c>
@@ -5009,7 +4824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>44.7</v>
       </c>
@@ -5035,7 +4850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>40.9</v>
       </c>
@@ -5061,7 +4876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>29.7</v>
       </c>
@@ -5087,7 +4902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>33</v>
       </c>
@@ -5113,7 +4928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>43</v>
       </c>
@@ -5139,7 +4954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>39.9</v>
       </c>
@@ -5165,7 +4980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>25.3</v>
       </c>
@@ -5191,7 +5006,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>18</v>
       </c>
@@ -5217,7 +5032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>17.7</v>
       </c>
@@ -5243,7 +5058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>24.1</v>
       </c>
@@ -5269,7 +5084,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>30.4</v>
       </c>
@@ -5295,7 +5110,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>26.9</v>
       </c>
@@ -5321,7 +5136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>22.1</v>
       </c>
@@ -5347,7 +5162,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>24.7</v>
       </c>
@@ -5373,7 +5188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>21.4</v>
       </c>
@@ -5399,7 +5214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>20.5</v>
       </c>
@@ -5425,7 +5240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>16.3</v>
       </c>
@@ -5451,7 +5266,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>24.4</v>
       </c>
@@ -5477,7 +5292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>15.7</v>
       </c>
@@ -5503,7 +5318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>34.700000000000003</v>
       </c>
@@ -5529,7 +5344,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>19.7</v>
       </c>
@@ -5555,7 +5370,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>21.8</v>
       </c>
@@ -5581,7 +5396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>25.3</v>
       </c>
@@ -5607,7 +5422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>38</v>
       </c>
@@ -5633,7 +5448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>22.1</v>
       </c>
@@ -5659,7 +5474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>30.2</v>
       </c>
@@ -5685,7 +5500,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>26.9</v>
       </c>
@@ -5711,7 +5526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>37.5</v>
       </c>
@@ -5737,7 +5552,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>26.9</v>
       </c>
@@ -5763,7 +5578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>24.7</v>
       </c>
@@ -5789,7 +5604,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>34.9</v>
       </c>
@@ -5815,7 +5630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>29.4</v>
       </c>
@@ -5841,7 +5656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>38.299999999999997</v>
       </c>
@@ -5867,7 +5682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>28.9</v>
       </c>
@@ -5893,7 +5708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>45.8</v>
       </c>
@@ -5919,7 +5734,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>30.6</v>
       </c>
@@ -5945,7 +5760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>26.3</v>
       </c>
@@ -5971,7 +5786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>38.799999999999997</v>
       </c>
@@ -5997,7 +5812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>41.8</v>
       </c>
@@ -6023,7 +5838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>30.1</v>
       </c>
@@ -6049,7 +5864,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>45.5</v>
       </c>
@@ -6075,7 +5890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>32.6</v>
       </c>
@@ -6101,7 +5916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>11.4</v>
       </c>
@@ -6127,7 +5942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>35.4</v>
       </c>
@@ -6153,7 +5968,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>18.600000000000001</v>
       </c>
@@ -6179,7 +5994,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>31.1</v>
       </c>
@@ -6205,7 +6020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>32.299999999999997</v>
       </c>
@@ -6231,7 +6046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>22.4</v>
       </c>
@@ -6257,7 +6072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>24.1</v>
       </c>
@@ -6283,7 +6098,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>31.1</v>
       </c>
@@ -6309,7 +6124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>33.200000000000003</v>
       </c>
@@ -6335,7 +6150,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>24.4</v>
       </c>
@@ -6361,7 +6176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>21.7</v>
       </c>
@@ -6387,7 +6202,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>20.7</v>
       </c>
@@ -6413,7 +6228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>17.399999999999999</v>
       </c>
@@ -6439,7 +6254,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>15.9</v>
       </c>
@@ -6465,7 +6280,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>35.299999999999997</v>
       </c>
@@ -6491,7 +6306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>15.8</v>
       </c>
@@ -6517,7 +6332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>22.2</v>
       </c>
@@ -6543,7 +6358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>19.399999999999999</v>
       </c>
@@ -6569,7 +6384,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>17.8</v>
       </c>
@@ -6595,7 +6410,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>30.7</v>
       </c>
@@ -6621,7 +6436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>22.6</v>
       </c>
@@ -6647,7 +6462,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>28.4</v>
       </c>
@@ -6673,7 +6488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>40.4</v>
       </c>
@@ -6699,7 +6514,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>35.6</v>
       </c>
@@ -6725,7 +6540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>35.6</v>
       </c>
@@ -6751,7 +6566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>28.7</v>
       </c>
@@ -6777,7 +6592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>44.4</v>
       </c>
@@ -6803,7 +6618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>44</v>
       </c>
@@ -6829,7 +6644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>32.799999999999997</v>
       </c>
@@ -6855,7 +6670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>36.799999999999997</v>
       </c>
@@ -6881,7 +6696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>34.5</v>
       </c>
@@ -6907,7 +6722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>26.7</v>
       </c>
@@ -6933,7 +6748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>28.2</v>
       </c>
@@ -6959,7 +6774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>29.3</v>
       </c>
@@ -6985,7 +6800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>30.8</v>
       </c>
@@ -7011,7 +6826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>35.5</v>
       </c>
@@ -7037,7 +6852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>27.9</v>
       </c>
@@ -7063,7 +6878,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>34.799999999999997</v>
       </c>
@@ -7089,7 +6904,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>24.3</v>
       </c>
@@ -7115,7 +6930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>22.1</v>
       </c>
@@ -7141,7 +6956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>33.299999999999997</v>
       </c>
@@ -7164,7 +6979,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>18.899999999999999</v>
       </c>
@@ -7190,7 +7005,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>21.8</v>
       </c>
@@ -7216,7 +7031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>12.4</v>
       </c>
@@ -7242,7 +7057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>18</v>
       </c>
@@ -7268,7 +7083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>20.3</v>
       </c>
@@ -7291,7 +7106,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>26.2</v>
       </c>
@@ -7317,7 +7132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>11.5</v>
       </c>
@@ -7343,7 +7158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>26.6</v>
       </c>
@@ -7369,7 +7184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>25.3</v>
       </c>
@@ -7395,7 +7210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>27.5</v>
       </c>
@@ -7421,7 +7236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>21.4</v>
       </c>
@@ -7447,7 +7262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>28.1</v>
       </c>
@@ -7473,7 +7288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>20.3</v>
       </c>
@@ -7499,7 +7314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>17.600000000000001</v>
       </c>
@@ -7525,7 +7340,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>24.2</v>
       </c>
@@ -7551,7 +7366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>29.3</v>
       </c>
@@ -7577,7 +7392,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>33.200000000000003</v>
       </c>
@@ -7603,7 +7418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>38.799999999999997</v>
       </c>
@@ -7629,7 +7444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>33.1</v>
       </c>
@@ -7655,7 +7470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>29.4</v>
       </c>
@@ -7681,7 +7496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>24</v>
       </c>
@@ -7707,7 +7522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>27.5</v>
       </c>
@@ -7733,7 +7548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>29.6</v>
       </c>
@@ -7759,7 +7574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>27.2</v>
       </c>
@@ -7785,7 +7600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>36.200000000000003</v>
       </c>
@@ -7811,7 +7626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>45.6</v>
       </c>
@@ -7837,7 +7652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>32.9</v>
       </c>
@@ -7863,7 +7678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>10.199999999999999</v>
       </c>
@@ -7889,7 +7704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>24.6</v>
       </c>
@@ -7915,7 +7730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>20.6</v>
       </c>
@@ -7941,7 +7756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>27.5</v>
       </c>
@@ -7967,7 +7782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>12.7</v>
       </c>
@@ -7993,7 +7808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>31.2</v>
       </c>
@@ -8019,7 +7834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>24.4</v>
       </c>
@@ -8045,7 +7860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>26.4</v>
       </c>
@@ -8071,7 +7886,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>21.7</v>
       </c>
@@ -8097,7 +7912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>14.7</v>
       </c>
@@ -8123,7 +7938,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>18.5</v>
       </c>
@@ -8149,7 +7964,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>17.3</v>
       </c>
@@ -8175,7 +7990,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>26.3</v>
       </c>
@@ -8201,7 +8016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>20.7</v>
       </c>
@@ -8227,7 +8042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>29.6</v>
       </c>
@@ -8253,7 +8068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>11.5</v>
       </c>
@@ -8279,7 +8094,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>40.1</v>
       </c>
@@ -8305,7 +8120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>40.6</v>
       </c>
@@ -8331,7 +8146,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>19.399999999999999</v>
       </c>
@@ -8357,7 +8172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>39.700000000000003</v>
       </c>
@@ -8383,7 +8198,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>40.299999999999997</v>
       </c>
@@ -8409,7 +8224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>39.200000000000003</v>
       </c>
@@ -8435,7 +8250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>30.5</v>
       </c>
@@ -8461,7 +8276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>34.5</v>
       </c>
@@ -8487,7 +8302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>38.9</v>
       </c>
@@ -8513,7 +8328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>27.4</v>
       </c>
@@ -8539,7 +8354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>38.6</v>
       </c>
@@ -8565,7 +8380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>27.5</v>
       </c>
@@ -8591,7 +8406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>34.799999999999997</v>
       </c>
@@ -8617,7 +8432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>36.5</v>
       </c>
@@ -8643,7 +8458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>45.8</v>
       </c>
@@ -8669,7 +8484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>14.1</v>
       </c>
@@ -8695,7 +8510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>23.3</v>
       </c>
@@ -8721,7 +8536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>17.399999999999999</v>
       </c>
@@ -8747,7 +8562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>21.5</v>
       </c>
@@ -8773,7 +8588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>18.5</v>
       </c>
@@ -8799,7 +8614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>19.399999999999999</v>
       </c>
@@ -8825,7 +8640,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>17.3</v>
       </c>
@@ -8851,7 +8666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>27</v>
       </c>
@@ -8877,7 +8692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>16.5</v>
       </c>
@@ -8903,7 +8718,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>26.8</v>
       </c>
@@ -8929,7 +8744,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>13.7</v>
       </c>
@@ -8955,7 +8770,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>26.7</v>
       </c>
@@ -8981,7 +8796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>31.9</v>
       </c>
@@ -9007,7 +8822,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>21.4</v>
       </c>
@@ -9030,7 +8845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>19.899999999999999</v>
       </c>
@@ -9056,7 +8871,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>24.4</v>
       </c>
@@ -9082,7 +8897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>39.200000000000003</v>
       </c>
@@ -9108,7 +8923,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>37.700000000000003</v>
       </c>
@@ -9134,7 +8949,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>26.2</v>
       </c>
@@ -9160,7 +8975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>33.6</v>
       </c>
@@ -9186,7 +9001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>31.8</v>
       </c>
@@ -9212,7 +9027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>44.4</v>
       </c>
@@ -9238,7 +9053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>35.299999999999997</v>
       </c>
@@ -9264,7 +9079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>39.4</v>
       </c>
@@ -9290,7 +9105,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>29.4</v>
       </c>
@@ -9316,7 +9131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>25.6</v>
       </c>
@@ -9342,7 +9157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>24.4</v>
       </c>
@@ -9368,7 +9183,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>18.7</v>
       </c>
@@ -9394,7 +9209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>22.2</v>
       </c>
@@ -9420,7 +9235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>23.4</v>
       </c>
@@ -9446,7 +9261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>31.9</v>
       </c>
@@ -9472,7 +9287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>23.3</v>
       </c>
@@ -9498,7 +9313,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>15.8</v>
       </c>
@@ -9524,7 +9339,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>24.8</v>
       </c>
@@ -9550,7 +9365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>20.9</v>
       </c>
@@ -9576,7 +9391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>17.600000000000001</v>
       </c>
@@ -9602,7 +9417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>18.5</v>
       </c>
@@ -9628,7 +9443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>26.6</v>
       </c>
@@ -9654,7 +9469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>25</v>
       </c>
@@ -9680,7 +9495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>32.9</v>
       </c>
@@ -9706,7 +9521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>23.4</v>
       </c>
@@ -9732,7 +9547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>19.100000000000001</v>
       </c>
@@ -9758,7 +9573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>20.399999999999999</v>
       </c>
@@ -9784,7 +9599,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>31.2</v>
       </c>
@@ -9807,7 +9622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>34.200000000000003</v>
       </c>
@@ -9833,7 +9648,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>35.6</v>
       </c>
@@ -9856,7 +9671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>31.4</v>
       </c>
@@ -9882,7 +9697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>28.9</v>
       </c>
@@ -9908,7 +9723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>36.6</v>
       </c>
@@ -9934,7 +9749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>25.8</v>
       </c>
@@ -9960,7 +9775,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>39.299999999999997</v>
       </c>
@@ -9986,7 +9801,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>39.9</v>
       </c>
@@ -10009,7 +9824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>34.700000000000003</v>
       </c>
@@ -10035,7 +9850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>34.799999999999997</v>
       </c>
@@ -10061,7 +9876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>36.6</v>
       </c>
@@ -10087,7 +9902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>27.4</v>
       </c>
@@ -10113,7 +9928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>32.200000000000003</v>
       </c>
@@ -10136,7 +9951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>27.1</v>
       </c>
@@ -10162,7 +9977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>35.200000000000003</v>
       </c>
@@ -10188,7 +10003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>27.5</v>
       </c>
@@ -10214,7 +10029,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>41</v>
       </c>
@@ -10240,7 +10055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>35.9</v>
       </c>
@@ -10266,7 +10081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>21.9</v>
       </c>
@@ -10292,7 +10107,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>23.1</v>
       </c>
@@ -10318,7 +10133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>15.2</v>
       </c>
@@ -10344,7 +10159,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>21.5</v>
       </c>
@@ -10370,7 +10185,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>28</v>
       </c>
@@ -10396,7 +10211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>17.7</v>
       </c>
@@ -10422,7 +10237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>22</v>
       </c>
@@ -10448,7 +10263,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>19.2</v>
       </c>
@@ -10474,7 +10289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>22.7</v>
       </c>
@@ -10500,7 +10315,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>20.100000000000001</v>
       </c>
@@ -10526,7 +10341,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>31.3</v>
       </c>
@@ -10552,7 +10367,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>27.8</v>
       </c>
@@ -10578,7 +10393,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>24</v>
       </c>
@@ -10604,7 +10419,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>31</v>
       </c>
@@ -10630,7 +10445,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>17.7</v>
       </c>
@@ -10656,7 +10471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>14.2</v>
       </c>
@@ -10682,7 +10497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>20.9</v>
       </c>
@@ -10708,7 +10523,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>19.2</v>
       </c>
@@ -10734,7 +10549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>38</v>
       </c>
@@ -10760,7 +10575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>35.9</v>
       </c>
@@ -10783,7 +10598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>40.799999999999997</v>
       </c>
@@ -10809,7 +10624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>30.7</v>
       </c>
@@ -10835,7 +10650,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>25.1</v>
       </c>
@@ -10861,7 +10676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>23.1</v>
       </c>
@@ -10887,7 +10702,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>31.7</v>
       </c>
@@ -10913,7 +10728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>25.7</v>
       </c>
@@ -10939,7 +10754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>42.1</v>
       </c>
@@ -10965,7 +10780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>45.6</v>
       </c>
@@ -10991,7 +10806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>35.5</v>
       </c>
@@ -11017,7 +10832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>34.6</v>
       </c>
@@ -11043,7 +10858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>40.4</v>
       </c>
@@ -11069,7 +10884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>30.5</v>
       </c>
@@ -11095,7 +10910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>43.6</v>
       </c>
@@ -11121,7 +10936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>40</v>
       </c>
@@ -11144,7 +10959,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>31.3</v>
       </c>
@@ -11170,7 +10985,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>11.2</v>
       </c>
@@ -11196,7 +11011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>25.5</v>
       </c>
@@ -11222,7 +11037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>25</v>
       </c>
@@ -11248,7 +11063,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>17.100000000000001</v>
       </c>
@@ -11274,7 +11089,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>34.5</v>
       </c>
@@ -11300,7 +11115,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>18</v>
       </c>
@@ -11326,7 +11141,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>23.3</v>
       </c>
@@ -11352,7 +11167,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>16.2</v>
       </c>
@@ -11378,7 +11193,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>25.4</v>
       </c>
@@ -11404,7 +11219,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>18.5</v>
       </c>
@@ -11427,7 +11242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>22.3</v>
       </c>
@@ -11453,7 +11268,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>16</v>
       </c>
@@ -11479,7 +11294,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>10.6</v>
       </c>
@@ -11505,7 +11320,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>20.6</v>
       </c>
@@ -11531,7 +11346,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>21.1</v>
       </c>
@@ -11557,7 +11372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>30.8</v>
       </c>
@@ -11583,7 +11398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>29.6</v>
       </c>
@@ -11609,7 +11424,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>36.299999999999997</v>
       </c>
@@ -11635,7 +11450,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>33.4</v>
       </c>
@@ -11661,7 +11476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>44.2</v>
       </c>
@@ -11687,7 +11502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>34.799999999999997</v>
       </c>
@@ -11713,7 +11528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>34</v>
       </c>
@@ -11739,7 +11554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>33</v>
       </c>
@@ -11765,7 +11580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>34.4</v>
       </c>
@@ -11791,7 +11606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>29</v>
       </c>
@@ -11817,7 +11632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>15.9</v>
       </c>
@@ -11843,7 +11658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>22.2</v>
       </c>
@@ -11869,7 +11684,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>22.7</v>
       </c>
@@ -11895,7 +11710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>32.5</v>
       </c>
@@ -11921,7 +11736,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>22.8</v>
       </c>
@@ -11947,7 +11762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>23.8</v>
       </c>
@@ -11973,7 +11788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>17.399999999999999</v>
       </c>
@@ -11999,7 +11814,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>22.6</v>
       </c>
@@ -12025,7 +11840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>25.9</v>
       </c>
@@ -12051,7 +11866,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>19.2</v>
       </c>
@@ -12077,7 +11892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>23.1</v>
       </c>
@@ -12103,7 +11918,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>16.3</v>
       </c>
@@ -12129,7 +11944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>17.2</v>
       </c>
@@ -12155,7 +11970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>34.200000000000003</v>
       </c>
@@ -12181,7 +11996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>19.2</v>
       </c>
@@ -12207,7 +12022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>23.8</v>
       </c>
@@ -12233,7 +12048,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>33.799999999999997</v>
       </c>
@@ -12259,7 +12074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>39.799999999999997</v>
       </c>
@@ -12285,7 +12100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>36.299999999999997</v>
       </c>
@@ -12311,7 +12126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>25.2</v>
       </c>
@@ -12337,7 +12152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>41.9</v>
       </c>
@@ -12363,7 +12178,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>24.3</v>
       </c>
@@ -12389,7 +12204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>26.3</v>
       </c>
@@ -12415,7 +12230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>42.7</v>
       </c>
@@ -12441,7 +12256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>41.8</v>
       </c>
@@ -12467,7 +12282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>26.3</v>
       </c>
@@ -12493,7 +12308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>34</v>
       </c>
@@ -12519,7 +12334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>40.200000000000003</v>
       </c>
@@ -12545,7 +12360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>30.8</v>
       </c>
@@ -12571,7 +12386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>40</v>
       </c>
@@ -12607,363 +12422,351 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE8A746-C358-490F-985F-C2AE3E23621E}">
-  <dimension ref="A1:H383"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:H343"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.29296875" style="4" customWidth="1"/>
-    <col min="2" max="8" width="12.3515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" customWidth="1"/>
+    <col min="2" max="8" width="12.33203125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="e" cm="1" vm="2">
         <f t="array" ref="A1">_xlfn._xlws.PY(1,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="e" cm="1" vm="3">
         <f t="array" ref="A10">_xlfn._xlws.PY(2,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="e" cm="1" vm="4">
         <f t="array" ref="A22">_xlfn._xlws.PY(3,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" s="4" t="e" cm="1" vm="5">
         <f t="array" ref="A36">_xlfn._xlws.PY(4,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" s="4" t="e" cm="1" vm="6">
         <f t="array" ref="A47">_xlfn._xlws.PY(5,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A63" s="4" t="e" cm="1" vm="7">
         <f t="array" ref="A63">_xlfn._xlws.PY(6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A79" s="4" t="e" cm="1" vm="8">
         <f t="array" ref="A79">_xlfn._xlws.PY(7,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A101" s="4" t="e" cm="1" vm="9">
-        <f t="array" ref="A101">_xlfn._xlws.PY(8,0)</f>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A99" s="4" t="e" cm="1" vm="9">
+        <f t="array" ref="A99">_xlfn._xlws.PY(8,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A114" s="4" t="e" cm="1" vm="10">
-        <f t="array" ref="A114">_xlfn._xlws.PY(9,0)</f>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A117" s="4" t="e" cm="1" vm="10">
+        <f t="array" ref="A117">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A132" s="4" t="e" cm="1" vm="11">
-        <f t="array" ref="A132">_xlfn._xlws.PY(10,0)</f>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A131" s="4" t="e" cm="1" vm="11">
+        <f t="array" ref="A131">_xlfn._xlws.PY(10,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A147" s="4" t="e" cm="1" vm="12">
-        <f t="array" ref="A147">_xlfn._xlws.PY(11,0)</f>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A143" s="4" t="e" cm="1" vm="12">
+        <f t="array" ref="A143">_xlfn._xlws.PY(11,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A163" s="4" t="e" cm="1" vm="13">
-        <f t="array" ref="A163">_xlfn._xlws.PY(12,0)</f>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A155" s="4" t="e" cm="1" vm="13">
+        <f t="array" ref="A155">_xlfn._xlws.PY(12,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A181" s="4" t="e" cm="1" vm="14">
-        <f t="array" ref="A181">_xlfn._xlws.PY(13,0)</f>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A177" s="4" t="e" cm="1" vm="14">
+        <f t="array" ref="A177">_xlfn._xlws.PY(13,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A195" s="4" t="e" cm="1" vm="15">
-        <f t="array" ref="A195">_xlfn._xlws.PY(14,0)</f>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A197" s="4" t="str" cm="1">
+        <f t="array" ref="A197:H204">_xlfn._xlws.PY(14,0)</f>
+        <v/>
+      </c>
+      <c r="B197" s="4" t="str">
+        <v>mpg</v>
+      </c>
+      <c r="C197" s="4" t="str">
+        <v>cylinders</v>
+      </c>
+      <c r="D197" s="4" t="str">
+        <v>displacement</v>
+      </c>
+      <c r="E197" s="4" t="str">
+        <v>horsepower</v>
+      </c>
+      <c r="F197" s="4" t="str">
+        <v>weight</v>
+      </c>
+      <c r="G197" s="4" t="str">
+        <v>acceleration</v>
+      </c>
+      <c r="H197" s="4" t="str">
+        <v>model_year</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A198" s="4" t="str">
+        <v>mpg</v>
+      </c>
+      <c r="B198" s="4">
+        <v>1</v>
+      </c>
+      <c r="C198" s="4">
+        <v>-0.78627226915628468</v>
+      </c>
+      <c r="D198" s="4">
+        <v>-0.74790943103350538</v>
+      </c>
+      <c r="E198" s="4">
+        <v>-0.69064315601834925</v>
+      </c>
+      <c r="F198" s="4">
+        <v>-0.75528713492250599</v>
+      </c>
+      <c r="G198" s="4">
+        <v>0.55894731397140851</v>
+      </c>
+      <c r="H198" s="4">
+        <v>-1.8773081852925172E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A199" s="4" t="str">
+        <v>cylinders</v>
+      </c>
+      <c r="B199" s="4">
+        <v>-0.78627226915628468</v>
+      </c>
+      <c r="C199" s="4">
+        <v>1</v>
+      </c>
+      <c r="D199" s="4">
+        <v>0.95090061798664194</v>
+      </c>
+      <c r="E199" s="4">
+        <v>0.90099373386577719</v>
+      </c>
+      <c r="F199" s="4">
+        <v>0.91267795874949453</v>
+      </c>
+      <c r="G199" s="4">
+        <v>-0.64366089242948299</v>
+      </c>
+      <c r="H199" s="4">
+        <v>-9.1942664715094335E-3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A200" s="4" t="str">
+        <v>displacement</v>
+      </c>
+      <c r="B200" s="4">
+        <v>-0.74790943103350538</v>
+      </c>
+      <c r="C200" s="4">
+        <v>0.95090061798664194</v>
+      </c>
+      <c r="D200" s="4">
+        <v>1</v>
+      </c>
+      <c r="E200" s="4">
+        <v>0.89247642477052325</v>
+      </c>
+      <c r="F200" s="4">
+        <v>0.87199796965664167</v>
+      </c>
+      <c r="G200" s="4">
+        <v>-0.62323054423620383</v>
+      </c>
+      <c r="H200" s="4">
+        <v>2.2402916481058133E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A201" s="4" t="str">
+        <v>horsepower</v>
+      </c>
+      <c r="B201" s="4">
+        <v>-0.69064315601834925</v>
+      </c>
+      <c r="C201" s="4">
+        <v>0.90099373386577719</v>
+      </c>
+      <c r="D201" s="4">
+        <v>0.89247642477052325</v>
+      </c>
+      <c r="E201" s="4">
+        <v>1</v>
+      </c>
+      <c r="F201" s="4">
+        <v>0.83464897621101919</v>
+      </c>
+      <c r="G201" s="4">
+        <v>-0.57729736467931814</v>
+      </c>
+      <c r="H201" s="4">
+        <v>3.109573764826493E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A202" s="4" t="str">
+        <v>weight</v>
+      </c>
+      <c r="B202" s="4">
+        <v>-0.75528713492250599</v>
+      </c>
+      <c r="C202" s="4">
+        <v>0.91267795874949453</v>
+      </c>
+      <c r="D202" s="4">
+        <v>0.87199796965664167</v>
+      </c>
+      <c r="E202" s="4">
+        <v>0.83464897621101919</v>
+      </c>
+      <c r="F202" s="4">
+        <v>1</v>
+      </c>
+      <c r="G202" s="4">
+        <v>-0.61105286772043321</v>
+      </c>
+      <c r="H202" s="4">
+        <v>-1.0367952063320311E-2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A203" s="4" t="str">
+        <v>acceleration</v>
+      </c>
+      <c r="B203" s="4">
+        <v>0.55894731397140851</v>
+      </c>
+      <c r="C203" s="4">
+        <v>-0.64366089242948299</v>
+      </c>
+      <c r="D203" s="4">
+        <v>-0.62323054423620383</v>
+      </c>
+      <c r="E203" s="4">
+        <v>-0.57729736467931814</v>
+      </c>
+      <c r="F203" s="4">
+        <v>-0.61105286772043321</v>
+      </c>
+      <c r="G203" s="4">
+        <v>1</v>
+      </c>
+      <c r="H203" s="4">
+        <v>1.7399828573187046E-2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A204" s="4" t="str">
+        <v>model_year</v>
+      </c>
+      <c r="B204" s="4">
+        <v>-1.8773081852925172E-2</v>
+      </c>
+      <c r="C204" s="4">
+        <v>-9.1942664715094335E-3</v>
+      </c>
+      <c r="D204" s="4">
+        <v>2.2402916481058133E-2</v>
+      </c>
+      <c r="E204" s="4">
+        <v>3.109573764826493E-2</v>
+      </c>
+      <c r="F204" s="4">
+        <v>-1.0367952063320311E-2</v>
+      </c>
+      <c r="G204" s="4">
+        <v>1.7399828573187046E-2</v>
+      </c>
+      <c r="H204" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A207" s="4" t="e" cm="1" vm="15">
+        <f t="array" ref="A207">_xlfn._xlws.PY(15,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A217" s="4" t="e" cm="1" vm="16">
-        <f t="array" ref="A217">_xlfn._xlws.PY(15,0)</f>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A223" s="4" t="e" cm="1" vm="16">
+        <f t="array" ref="A223">_xlfn._xlws.PY(16,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A237" s="4" t="str" cm="1">
-        <f t="array" ref="A237:H244">_xlfn._xlws.PY(16,0)</f>
-        <v/>
-      </c>
-      <c r="B237" s="4" t="str">
-        <v>mpg</v>
-      </c>
-      <c r="C237" s="4" t="str">
-        <v>cylinders</v>
-      </c>
-      <c r="D237" s="4" t="str">
-        <v>displacement</v>
-      </c>
-      <c r="E237" s="4" t="str">
-        <v>horsepower</v>
-      </c>
-      <c r="F237" s="4" t="str">
-        <v>weight</v>
-      </c>
-      <c r="G237" s="4" t="str">
-        <v>acceleration</v>
-      </c>
-      <c r="H237" s="4" t="str">
-        <v>model_year</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A238" s="4" t="str">
-        <v>mpg</v>
-      </c>
-      <c r="B238" s="4">
-        <v>1</v>
-      </c>
-      <c r="C238" s="4">
-        <v>-0.78627226915628468</v>
-      </c>
-      <c r="D238" s="4">
-        <v>-0.74790943103350538</v>
-      </c>
-      <c r="E238" s="4">
-        <v>-0.69064315601834925</v>
-      </c>
-      <c r="F238" s="4">
-        <v>-0.75528713492250599</v>
-      </c>
-      <c r="G238" s="4">
-        <v>0.55894731397140851</v>
-      </c>
-      <c r="H238" s="4">
-        <v>-1.8773081852925172E-2</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A239" s="4" t="str">
-        <v>cylinders</v>
-      </c>
-      <c r="B239" s="4">
-        <v>-0.78627226915628468</v>
-      </c>
-      <c r="C239" s="4">
-        <v>1</v>
-      </c>
-      <c r="D239" s="4">
-        <v>0.95090061798664194</v>
-      </c>
-      <c r="E239" s="4">
-        <v>0.90099373386577719</v>
-      </c>
-      <c r="F239" s="4">
-        <v>0.91267795874949453</v>
-      </c>
-      <c r="G239" s="4">
-        <v>-0.64366089242948299</v>
-      </c>
-      <c r="H239" s="4">
-        <v>-9.1942664715094335E-3</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A240" s="4" t="str">
-        <v>displacement</v>
-      </c>
-      <c r="B240" s="4">
-        <v>-0.74790943103350538</v>
-      </c>
-      <c r="C240" s="4">
-        <v>0.95090061798664194</v>
-      </c>
-      <c r="D240" s="4">
-        <v>1</v>
-      </c>
-      <c r="E240" s="4">
-        <v>0.89247642477052325</v>
-      </c>
-      <c r="F240" s="4">
-        <v>0.87199796965664167</v>
-      </c>
-      <c r="G240" s="4">
-        <v>-0.62323054423620383</v>
-      </c>
-      <c r="H240" s="4">
-        <v>2.2402916481058133E-2</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A241" s="4" t="str">
-        <v>horsepower</v>
-      </c>
-      <c r="B241" s="4">
-        <v>-0.69064315601834925</v>
-      </c>
-      <c r="C241" s="4">
-        <v>0.90099373386577719</v>
-      </c>
-      <c r="D241" s="4">
-        <v>0.89247642477052325</v>
-      </c>
-      <c r="E241" s="4">
-        <v>1</v>
-      </c>
-      <c r="F241" s="4">
-        <v>0.83464897621101919</v>
-      </c>
-      <c r="G241" s="4">
-        <v>-0.57729736467931814</v>
-      </c>
-      <c r="H241" s="4">
-        <v>3.109573764826493E-2</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A242" s="4" t="str">
-        <v>weight</v>
-      </c>
-      <c r="B242" s="4">
-        <v>-0.75528713492250599</v>
-      </c>
-      <c r="C242" s="4">
-        <v>0.91267795874949453</v>
-      </c>
-      <c r="D242" s="4">
-        <v>0.87199796965664167</v>
-      </c>
-      <c r="E242" s="4">
-        <v>0.83464897621101919</v>
-      </c>
-      <c r="F242" s="4">
-        <v>1</v>
-      </c>
-      <c r="G242" s="4">
-        <v>-0.61105286772043321</v>
-      </c>
-      <c r="H242" s="4">
-        <v>-1.0367952063320311E-2</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A243" s="4" t="str">
-        <v>acceleration</v>
-      </c>
-      <c r="B243" s="4">
-        <v>0.55894731397140851</v>
-      </c>
-      <c r="C243" s="4">
-        <v>-0.64366089242948299</v>
-      </c>
-      <c r="D243" s="4">
-        <v>-0.62323054423620383</v>
-      </c>
-      <c r="E243" s="4">
-        <v>-0.57729736467931814</v>
-      </c>
-      <c r="F243" s="4">
-        <v>-0.61105286772043321</v>
-      </c>
-      <c r="G243" s="4">
-        <v>1</v>
-      </c>
-      <c r="H243" s="4">
-        <v>1.7399828573187046E-2</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A244" s="4" t="str">
-        <v>model_year</v>
-      </c>
-      <c r="B244" s="4">
-        <v>-1.8773081852925172E-2</v>
-      </c>
-      <c r="C244" s="4">
-        <v>-9.1942664715094335E-3</v>
-      </c>
-      <c r="D244" s="4">
-        <v>2.2402916481058133E-2</v>
-      </c>
-      <c r="E244" s="4">
-        <v>3.109573764826493E-2</v>
-      </c>
-      <c r="F244" s="4">
-        <v>-1.0367952063320311E-2</v>
-      </c>
-      <c r="G244" s="4">
-        <v>1.7399828573187046E-2</v>
-      </c>
-      <c r="H244" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A247" s="4" t="e" cm="1" vm="17">
-        <f t="array" ref="A247">_xlfn._xlws.PY(17,0)</f>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A240" s="4" t="e" cm="1" vm="17">
+        <f t="array" ref="A240">_xlfn._xlws.PY(17,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A263" s="4" t="e" cm="1" vm="18">
-        <f t="array" ref="A263">_xlfn._xlws.PY(18,0)</f>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A255" s="4" t="e" cm="1" vm="18">
+        <f t="array" ref="A255">_xlfn._xlws.PY(18,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A280" s="4" t="e" cm="1" vm="19">
-        <f t="array" ref="A280">_xlfn._xlws.PY(19,0)</f>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A270" s="4" t="e" cm="1" vm="19">
+        <f t="array" ref="A270">_xlfn._xlws.PY(19,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A295" s="4" t="e" cm="1" vm="20">
-        <f t="array" ref="A295">_xlfn._xlws.PY(20,0)</f>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A290" s="4" t="e" cm="1" vm="20">
+        <f t="array" ref="A290">_xlfn._xlws.PY(20,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A310" s="4" t="e" cm="1" vm="21">
-        <f t="array" ref="A310">_xlfn._xlws.PY(21,0)</f>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A306" s="4" t="e" cm="1" vm="21">
+        <f t="array" ref="A306">_xlfn._xlws.PY(21,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A330" s="4" t="e" cm="1" vm="22">
-        <f t="array" ref="A330">_xlfn._xlws.PY(22,0)</f>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A324" s="4" t="e" cm="1" vm="22">
+        <f t="array" ref="A324">_xlfn._xlws.PY(22,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A346" s="4" t="e" cm="1" vm="23">
-        <f t="array" ref="A346">_xlfn._xlws.PY(23,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A364" s="4" t="e" cm="1" vm="24">
-        <f t="array" ref="A364">_xlfn._xlws.PY(24,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A383" s="4" t="e" cm="1" vm="25">
-        <f t="array" ref="A383">_xlfn._xlws.PY(25,0)</f>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A343" s="4" t="e" cm="1" vm="23">
+        <f t="array" ref="A343">_xlfn._xlws.PY(23,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
